--- a/Docs/PerRepassarAccionsEnDolars.xlsx
+++ b/Docs/PerRepassarAccionsEnDolars.xlsx
@@ -4,12 +4,10 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="84" windowWidth="22980" windowHeight="10056"/>
+    <workbookView xWindow="0" yWindow="80" windowWidth="22980" windowHeight="10060"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="125725"/>
 </workbook>
@@ -510,13 +508,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="B3:K21"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="10.44140625" customWidth="1"/>
-    <col min="3" max="3" width="4.109375" customWidth="1"/>
-    <col min="8" max="8" width="14.6640625" customWidth="1"/>
-    <col min="9" max="10" width="11.109375" customWidth="1"/>
-    <col min="11" max="11" width="11.21875" customWidth="1"/>
+    <col min="2" max="2" width="10.453125" customWidth="1"/>
+    <col min="3" max="3" width="4.08984375" customWidth="1"/>
+    <col min="8" max="8" width="14.6328125" customWidth="1"/>
+    <col min="9" max="10" width="11.08984375" customWidth="1"/>
+    <col min="11" max="11" width="11.1796875" customWidth="1"/>
     <col min="12" max="12" width="16" customWidth="1"/>
   </cols>
   <sheetData>
@@ -828,22 +826,4 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>